--- a/nr-publish-shapshot-6/ig/StructureDefinition-as-dp-organization.xlsx
+++ b/nr-publish-shapshot-6/ig/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-21T14:10:07+00:00</t>
+    <t>2025-03-21T14:10:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-publish-shapshot-6/ig/StructureDefinition-as-dp-organization.xlsx
+++ b/nr-publish-shapshot-6/ig/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-21T14:10:28+00:00</t>
+    <t>2025-03-21T14:19:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-publish-shapshot-6/ig/StructureDefinition-as-dp-organization.xlsx
+++ b/nr-publish-shapshot-6/ig/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-21T14:19:07+00:00</t>
+    <t>2025-03-21T14:50:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-publish-shapshot-6/ig/StructureDefinition-as-dp-organization.xlsx
+++ b/nr-publish-shapshot-6/ig/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-21T14:50:29+00:00</t>
+    <t>2025-03-21T16:09:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-publish-shapshot-6/ig/StructureDefinition-as-dp-organization.xlsx
+++ b/nr-publish-shapshot-6/ig/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-21T16:09:25+00:00</t>
+    <t>2025-03-22T07:48:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
